--- a/SBM-corps-FHIR/ig/ValueSet-fr-doc-vs-vac-type.xlsx
+++ b/SBM-corps-FHIR/ig/ValueSet-fr-doc-vs-vac-type.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,10 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>FR ValueSet Type de vaccination : 
- - JDV_HL7_ActSubstanceAdministrationImmunizationCode_CISIS (2.16.840.1.113883.1.11.19709). Il permet d’indiquer si l’entrée concerne une vaccination. 
-OU
- - JDV_AbsentOrUnknownImmunization_CISIS (1.2.250.1.213.1.1.5.666)</t>
+    <t>ValueSet pour le type de vaccination. Il permet d’indiquer si l’entrée concerne une vaccination ou si l’information relative à la vaccination est absente ou inconnue.</t>
   </si>
   <si>
     <t>Purpose</t>
